--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,24 @@
         <is>
           <t>가스켓재고</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,24 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,24 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -501,7 +501,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -483,7 +483,7 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -465,7 +465,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -465,7 +465,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,24 @@
       </c>
       <c r="D4" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,24 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HP-F8703</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master.xlsx
+++ b/filter_master.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
